--- a/10-projects/11-제조사-직납-출고-대시보드/app/data/milkrun-source/2026년 쿠팡 후행물류비 절감.xlsx
+++ b/10-projects/11-제조사-직납-출고-대시보드/app/data/milkrun-source/2026년 쿠팡 후행물류비 절감.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\공유 드라이브\HQ_Team_SCM\SCM_공용\★성과측정지표(KPI)\2026년\물류운영\쿠팡 비용 절감\밀크런&amp;쉽먼트\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB4FBE8-9EBC-4C1B-9B46-CB798B2DB1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC1C535-C0F9-492B-9072-28D952E75D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{4AD39F71-AE63-4F13-8C1D-D77D65D69EA2}"/>
   </bookViews>
@@ -5908,6 +5908,9 @@
                 <c:pt idx="17">
                   <c:v>2232552430</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>2581068673</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6148,6 +6151,9 @@
                 <c:pt idx="17">
                   <c:v>5499750</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>7046580</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6410,7 +6416,7 @@
                   <c:v>2.4634359874809299E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>2.7301017108582759E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
@@ -6944,7 +6950,7 @@
                   <c:v>94761100</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>90280600</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
@@ -7174,7 +7180,7 @@
                   <c:v>57535341</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>61703929</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
@@ -9025,7 +9031,7 @@
                         <c:v>94761100</c:v>
                       </c:pt>
                       <c:pt idx="18">
-                        <c:v>0</c:v>
+                        <c:v>90280600</c:v>
                       </c:pt>
                       <c:pt idx="19">
                         <c:v>0</c:v>
@@ -12568,6 +12574,9 @@
                 <c:pt idx="17">
                   <c:v>2095516400</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>2536627026</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -12754,6 +12763,9 @@
                 <c:pt idx="17">
                   <c:v>22756000</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>26445000</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -13016,7 +13028,7 @@
                   <c:v>1.0859375760552388E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>1.0425261470820582E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
@@ -19347,7 +19359,9 @@
       <c r="U6" s="10">
         <v>2232552430</v>
       </c>
-      <c r="V6" s="10"/>
+      <c r="V6" s="10">
+        <v>2581068673</v>
+      </c>
       <c r="W6" s="11"/>
       <c r="X6" s="21"/>
       <c r="Y6" s="30"/>
@@ -19355,7 +19369,7 @@
       <c r="AA6" s="30"/>
       <c r="AB6" s="10">
         <f>SUM(P6:AA6)</f>
-        <v>13220954951</v>
+        <v>15802023624</v>
       </c>
       <c r="AC6" s="27"/>
     </row>
@@ -19419,7 +19433,9 @@
       <c r="U7" s="12">
         <v>5499750</v>
       </c>
-      <c r="V7" s="13"/>
+      <c r="V7" s="13">
+        <v>7046580</v>
+      </c>
       <c r="W7" s="14"/>
       <c r="X7" s="22"/>
       <c r="Y7" s="31"/>
@@ -19427,7 +19443,7 @@
       <c r="AA7" s="31"/>
       <c r="AB7" s="13">
         <f>SUM(P7:AA7)</f>
-        <v>52298535</v>
+        <v>59345115</v>
       </c>
       <c r="AC7" s="27"/>
       <c r="AD7" s="5"/>
@@ -19509,9 +19525,9 @@
         <f t="shared" si="1"/>
         <v>2.4634359874809299E-3</v>
       </c>
-      <c r="V8" s="15" t="e">
+      <c r="V8" s="15">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>2.7301017108582759E-3</v>
       </c>
       <c r="W8" s="15" t="e">
         <f t="shared" si="1"/>
@@ -19535,7 +19551,7 @@
       </c>
       <c r="AB8" s="86">
         <f>AB7/AB6</f>
-        <v>3.9557305197567647E-3</v>
+        <v>3.7555389367895302E-3</v>
       </c>
       <c r="AD8" s="4"/>
     </row>
@@ -19600,7 +19616,9 @@
       <c r="U9" s="10">
         <v>2095516400</v>
       </c>
-      <c r="V9" s="10"/>
+      <c r="V9" s="10">
+        <v>2536627026</v>
+      </c>
       <c r="W9" s="10"/>
       <c r="X9" s="21"/>
       <c r="Y9" s="30"/>
@@ -19608,7 +19626,7 @@
       <c r="AA9" s="30"/>
       <c r="AB9" s="10">
         <f>SUM(P9:AA9)</f>
-        <v>11998631800</v>
+        <v>14535258826</v>
       </c>
       <c r="AC9" s="27"/>
       <c r="AD9" s="4"/>
@@ -19673,7 +19691,9 @@
       <c r="U10" s="12">
         <v>22756000</v>
       </c>
-      <c r="V10" s="13"/>
+      <c r="V10" s="13">
+        <v>26445000</v>
+      </c>
       <c r="W10" s="13"/>
       <c r="X10" s="22"/>
       <c r="Y10" s="31"/>
@@ -19681,7 +19701,7 @@
       <c r="AA10" s="31"/>
       <c r="AB10" s="13">
         <f>SUM(P10:AA10)</f>
-        <v>125734000</v>
+        <v>152179000</v>
       </c>
       <c r="AC10" s="27"/>
       <c r="AD10" s="5"/>
@@ -19763,9 +19783,9 @@
         <f t="shared" si="3"/>
         <v>1.0859375760552388E-2</v>
       </c>
-      <c r="V11" s="15" t="e">
+      <c r="V11" s="15">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>1.0425261470820582E-2</v>
       </c>
       <c r="W11" s="15" t="e">
         <f t="shared" si="3"/>
@@ -19789,7 +19809,7 @@
       </c>
       <c r="AB11" s="86">
         <f>AB10/AB9</f>
-        <v>1.0479028117189161E-2</v>
+        <v>1.0469645007475837E-2</v>
       </c>
       <c r="AD11" s="4"/>
     </row>
@@ -19874,7 +19894,7 @@
       </c>
       <c r="V12" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5117695699</v>
       </c>
       <c r="W12" s="17">
         <f t="shared" si="5"/>
@@ -19898,7 +19918,7 @@
       </c>
       <c r="AB12" s="87">
         <f t="shared" si="4"/>
-        <v>25219586751</v>
+        <v>30337282450</v>
       </c>
       <c r="AC12" s="27"/>
     </row>
@@ -19981,7 +20001,7 @@
       </c>
       <c r="V13" s="18">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>33491580</v>
       </c>
       <c r="W13" s="18">
         <f t="shared" si="6"/>
@@ -20005,7 +20025,7 @@
       </c>
       <c r="AB13" s="88">
         <f t="shared" si="4"/>
-        <v>178032535</v>
+        <v>211524115</v>
       </c>
       <c r="AC13" s="27"/>
     </row>
@@ -20086,9 +20106,9 @@
         <f t="shared" si="8"/>
         <v>6.5284890582481799E-3</v>
       </c>
-      <c r="V14" s="19" t="e">
+      <c r="V14" s="19">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>6.5442695247676158E-3</v>
       </c>
       <c r="W14" s="19" t="e">
         <f t="shared" si="8"/>
@@ -20112,7 +20132,7 @@
       </c>
       <c r="AB14" s="89">
         <f>AB13/AB12</f>
-        <v>7.0592962825983142E-3</v>
+        <v>6.9724147292566738E-3</v>
       </c>
     </row>
     <row r="16" spans="2:30" ht="31.5" x14ac:dyDescent="0.3">
@@ -20281,7 +20301,9 @@
       <c r="U20" s="28">
         <v>61015100</v>
       </c>
-      <c r="V20" s="28"/>
+      <c r="V20" s="28">
+        <v>53145600</v>
+      </c>
       <c r="W20" s="28"/>
       <c r="X20" s="56"/>
       <c r="Y20" s="57"/>
@@ -20289,7 +20311,7 @@
       <c r="AA20" s="58"/>
       <c r="AB20" s="58">
         <f>SUM(P20:AA20)</f>
-        <v>306489600</v>
+        <v>359635200</v>
       </c>
       <c r="AO20" s="7"/>
       <c r="AP20" s="7"/>
@@ -20333,7 +20355,9 @@
       <c r="U21" s="51">
         <v>5499750</v>
       </c>
-      <c r="V21" s="52"/>
+      <c r="V21" s="52">
+        <v>7046580</v>
+      </c>
       <c r="W21" s="52"/>
       <c r="X21" s="53"/>
       <c r="Y21" s="54"/>
@@ -20341,7 +20365,7 @@
       <c r="AA21" s="55"/>
       <c r="AB21" s="55">
         <f t="shared" ref="AB21:AB34" si="9">SUM(P21:AA21)</f>
-        <v>52298535</v>
+        <v>59345115</v>
       </c>
       <c r="AL21" s="7"/>
       <c r="AM21" s="7"/>
@@ -20386,7 +20410,9 @@
       <c r="U22" s="41">
         <v>21755151</v>
       </c>
-      <c r="V22" s="42"/>
+      <c r="V22" s="42">
+        <v>21377719</v>
+      </c>
       <c r="W22" s="42"/>
       <c r="X22" s="43"/>
       <c r="Y22" s="44"/>
@@ -20394,7 +20420,7 @@
       <c r="AA22" s="45"/>
       <c r="AB22" s="45">
         <f t="shared" si="9"/>
-        <v>113759569</v>
+        <v>135137288</v>
       </c>
       <c r="AK22" t="s">
         <v>43</v>
@@ -20484,7 +20510,7 @@
       </c>
       <c r="V23" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>28424299</v>
       </c>
       <c r="W23" s="42">
         <f t="shared" si="11"/>
@@ -20508,7 +20534,7 @@
       </c>
       <c r="AB23" s="45">
         <f t="shared" si="9"/>
-        <v>166058104</v>
+        <v>194482403</v>
       </c>
       <c r="AK23" t="s">
         <v>33</v>
@@ -20603,7 +20629,7 @@
       </c>
       <c r="V24" s="69">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-24721301</v>
       </c>
       <c r="W24" s="69">
         <f t="shared" si="13"/>
@@ -20627,7 +20653,7 @@
       </c>
       <c r="AB24" s="72">
         <f t="shared" si="9"/>
-        <v>-140431496</v>
+        <v>-165152797</v>
       </c>
       <c r="AK24" t="s">
         <v>34</v>
@@ -20682,7 +20708,9 @@
       <c r="U25" s="28">
         <v>33746000</v>
       </c>
-      <c r="V25" s="28"/>
+      <c r="V25" s="28">
+        <v>37135000</v>
+      </c>
       <c r="W25" s="28"/>
       <c r="X25" s="56"/>
       <c r="Y25" s="57"/>
@@ -20690,7 +20718,7 @@
       <c r="AA25" s="58"/>
       <c r="AB25" s="58">
         <f t="shared" si="9"/>
-        <v>192251000</v>
+        <v>229386000</v>
       </c>
       <c r="AK25" t="s">
         <v>36</v>
@@ -20747,7 +20775,9 @@
       <c r="U26" s="51">
         <v>22756000</v>
       </c>
-      <c r="V26" s="52"/>
+      <c r="V26" s="52">
+        <v>26445000</v>
+      </c>
       <c r="W26" s="52"/>
       <c r="X26" s="53"/>
       <c r="Y26" s="54"/>
@@ -20755,7 +20785,7 @@
       <c r="AA26" s="55"/>
       <c r="AB26" s="55">
         <f t="shared" si="9"/>
-        <v>125734000</v>
+        <v>152179000</v>
       </c>
     </row>
     <row r="27" spans="2:42" x14ac:dyDescent="0.3">
@@ -20795,7 +20825,9 @@
       <c r="U27" s="41">
         <v>7524440</v>
       </c>
-      <c r="V27" s="42"/>
+      <c r="V27" s="42">
+        <v>6834630</v>
+      </c>
       <c r="W27" s="42"/>
       <c r="X27" s="43"/>
       <c r="Y27" s="44"/>
@@ -20803,7 +20835,7 @@
       <c r="AA27" s="45"/>
       <c r="AB27" s="45">
         <f t="shared" si="9"/>
-        <v>52170800</v>
+        <v>59005430</v>
       </c>
     </row>
     <row r="28" spans="2:42" x14ac:dyDescent="0.3">
@@ -20884,7 +20916,7 @@
       </c>
       <c r="V28" s="42">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>33279630</v>
       </c>
       <c r="W28" s="42">
         <f t="shared" si="15"/>
@@ -20908,7 +20940,7 @@
       </c>
       <c r="AB28" s="45">
         <f t="shared" si="9"/>
-        <v>178032800</v>
+        <v>211312430</v>
       </c>
     </row>
     <row r="29" spans="2:42" x14ac:dyDescent="0.3">
@@ -20990,7 +21022,7 @@
       </c>
       <c r="V29" s="69">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-3855370</v>
       </c>
       <c r="W29" s="69">
         <f t="shared" si="17"/>
@@ -21014,7 +21046,7 @@
       </c>
       <c r="AB29" s="72">
         <f>SUM(P29:AA29)</f>
-        <v>-14218200</v>
+        <v>-18073570</v>
       </c>
     </row>
     <row r="30" spans="2:42" x14ac:dyDescent="0.3">
@@ -21098,7 +21130,7 @@
       </c>
       <c r="V30" s="64">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>90280600</v>
       </c>
       <c r="W30" s="64">
         <f t="shared" si="19"/>
@@ -21122,7 +21154,7 @@
       </c>
       <c r="AB30" s="67">
         <f t="shared" si="9"/>
-        <v>498740600</v>
+        <v>589021200</v>
       </c>
     </row>
     <row r="31" spans="2:42" x14ac:dyDescent="0.3">
@@ -21204,7 +21236,7 @@
       </c>
       <c r="V31" s="60">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>33491580</v>
       </c>
       <c r="W31" s="60">
         <f t="shared" si="20"/>
@@ -21228,7 +21260,7 @@
       </c>
       <c r="AB31" s="63">
         <f t="shared" si="9"/>
-        <v>178032535</v>
+        <v>211524115</v>
       </c>
     </row>
     <row r="32" spans="2:42" x14ac:dyDescent="0.3">
@@ -21310,7 +21342,7 @@
       </c>
       <c r="V32" s="46">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>28212349</v>
       </c>
       <c r="W32" s="46">
         <f t="shared" si="21"/>
@@ -21334,7 +21366,7 @@
       </c>
       <c r="AB32" s="49">
         <f t="shared" si="9"/>
-        <v>165930369</v>
+        <v>194142718</v>
       </c>
     </row>
     <row r="33" spans="2:28" x14ac:dyDescent="0.3">
@@ -21416,7 +21448,7 @@
       </c>
       <c r="V33" s="46">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>61703929</v>
       </c>
       <c r="W33" s="46">
         <f t="shared" si="22"/>
@@ -21440,7 +21472,7 @@
       </c>
       <c r="AB33" s="49">
         <f t="shared" si="9"/>
-        <v>344090904</v>
+        <v>405794833</v>
       </c>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.3">
@@ -21522,7 +21554,7 @@
       </c>
       <c r="V34" s="69">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-28576671</v>
       </c>
       <c r="W34" s="69">
         <f t="shared" si="23"/>
@@ -21546,7 +21578,7 @@
       </c>
       <c r="AB34" s="72">
         <f t="shared" si="9"/>
-        <v>-154649696</v>
+        <v>-183226367</v>
       </c>
     </row>
     <row r="35" spans="2:28" ht="27.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -21557,7 +21589,7 @@
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="O35" s="91">
-        <f t="shared" ref="O35:U35" si="24">(-O34)/O30</f>
+        <f t="shared" ref="O35:V35" si="24">(-O34)/O30</f>
         <v>0.24059180182630671</v>
       </c>
       <c r="P35" s="91">
@@ -21584,10 +21616,14 @@
         <f t="shared" si="24"/>
         <v>0.39283797887529798</v>
       </c>
+      <c r="V35" s="91">
+        <f t="shared" si="24"/>
+        <v>0.3165316911938999</v>
+      </c>
       <c r="AA35" s="85"/>
       <c r="AB35" s="91">
         <f t="shared" ref="AB35" si="25">(-AB34)/AB30</f>
-        <v>0.31008042256836521</v>
+        <v>0.31106922297533601</v>
       </c>
     </row>
     <row r="36" spans="2:28" ht="27.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -21632,6 +21668,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>